--- a/website/assets/files/Agency Questionnaire Data Export 2025.xlsx
+++ b/website/assets/files/Agency Questionnaire Data Export 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pajak_hc\Work Folders\Desktop\Heather's Folders\Data Call\FY2025 Data Call\Website\Datasets\Exports of Questionnaires\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pajak_hc\Work Folders\Desktop\Heather's Folders\Data Call\FY2025 Data Call\UAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D91310B-C7B1-4739-8AD8-9082DCA68ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FE87FD-1E24-40F5-AAA8-1D0DFCF402EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025 Agency Survey Q&amp;A" sheetId="1" r:id="rId1"/>
@@ -1025,15 +1025,9 @@
     <t>State, Local, Tribal, and Other Assistance, Prisons and Detention, Litigation, Law Enforcement, Administrative, Technology, and Other</t>
   </si>
   <si>
-    <t>Women's Bureau, Veterans Employment Training Service - Federal Administration &amp; Uniformed Services Employment and Reemployment Rights Act (USERRA) Enforcement, Office of Workers' Compensation - Coal Mine Workers' Compensation, Office of Workers' Compensation - Longshore and Harbor Workers Compensation, Office of Labor-Management Standards, Mine Safety and Health Administration, Employment &amp; Training Administration - Work Opportunity Tax Credit Program (WOTC), Employment &amp; Training Administration - WIOA National Dislocated Worker Grants / WIA National Emergency Grants, Employment &amp; Training Administration - WIOA Dislocated Worker National Reserve Technical Assistance and Training, Employment &amp; Training Administration - Trade Adjustment Assistance Federal Unemployment Benefits and Allowances, Employment &amp; Training Administration - Temporary Labor Certification for Foreign Workers, Employment &amp; Training Administration - Permanent Labor Certification for Foreign Workers, Employment &amp; Training Administration - Job Corps, Employment &amp; Training Administration - Indian and Native American Program, Employment &amp; Training Administration - H-1B Job Training Grants, Employment &amp; Training Administration - Employment Service, Employment &amp; Training Administration - Dislocated Worker Employment and Training Activities - National Reserves Demos, Employment &amp; Training Administration - Community Projects, Bureau of Labor Statistics - Labor Force Statistics, Bureau of Labor Statistics - Compensation and Working Conditions</t>
-  </si>
-  <si>
     <t>Federal Transit Administration Washington Metro, Federal Transit Administration Formula Grants, Federal Railroad Administration Grants to National Railroad Passenger Corporation, Federal Aviation Administration Grants-in-Aid for Airports</t>
   </si>
   <si>
-    <t>Travel Pay Marine Corps – Integrated Automated Travel System (IATS), Military Retirement – Retired Pay, Military Retirement – Combat Related Special Compensation, Military Retirement – Annuitant Pay, Military Pay Department of Air Force (DAF) – Reserve, Military Pay Department of Air Force (DAF) – Air National Guard, Military Pay Department of Air Force (DAF) – Active Duty, Military Pay Army – Reserve, Military Pay Army – Active Duty, Commercial Pay – Transportation Financial Management System (TFMS), Commercial Pay – Standard Automated Voucher Examination System (SAVES), Commercial Pay – ONEPAY, Commercial Pay – Mechanization of Contract Administration Services (MOCAS), Commercial Pay – Integrated Accounts Payable System (IAPS), Commercial Pay – General Fund Enterprise Business System (GFEBS), Commercial Pay – Financial Accounting and Budgetary System (FABS), Commercial Pay – Enterprise Business System (EBS), Commercial Pay - U.S. Army Corps of Engineers (USACE), Civilian Pay – Department of Air Force (DAF)</t>
-  </si>
-  <si>
     <t>TRIO Upward Bound, TRIO Talent Search, TRIO Student Support Services, TRIO McNair Post-Baccalaureate Achievement, TRIO Educational Opportunity Centers, Transition Programs for Students with Intellectual Disabilities into Higher Education, Title I State Agency Program for Neglected and Delinquent Children and Youth, Title I Grants to Local Educational Agencies, Teacher Quality Partnership Grants, Teacher and School Leader Incentive Grants (formerly the Teacher Incentive Fund), Supporting Effective Instruction State Grants (formerly Improving Teacher Quality State Grants), Supporting Effective Educator Development Program, Supported Employment Services for Individuals with the Most Significant Disabilities, Student Support and Academic Enrichment Program, Strengthening Minority-Serving Institutions, Statewide Longitudinal Data Systems, Statewide Family Engagement Centers, Special Education Technical Assistance on State Data Collection, Special Education Technical Assistance and Dissemination to Improve Services and Results for Children with Disabilities, Special Education Preschool Grants, Special Education Parent Information Centers, Special Education Grants to States, Special Education Educational Technology Media, and Materials for Individuals with Disabilities, Special Education - State Personnel Development, Special Education - Special Olympics Education Programs, Special Education - Personnel Development to Improve Services and Results for Children with Disabilities, Rural Education, Research in Special Education, Rehabilitation Services Vocational Rehabilitation Grants to States, Rehabilitation Services Independent Living Services for Older Individuals Who are Blind, Rehabilitation Services Client Assistance Program, Ready-To-Learn Television, Program of Protection and Advocacy of Individual Rights, Personnel Compensation and Benefits, Native Hawaiian Education, National Technical Institute for the Deaf, National Resource Centers Program for Foreign Language and Area Studies or Foreign Language and International Studies Program and Foreign Language and Area Studies Fellowship Program, Minority Science and Engineering Improvement, Migrant Education State Grant Program, Migrant Education High School Equivalency Program, Migrant Education College Assistance Migrant Program, Javits Gifted and Talented Students Education, Indian Education Grants to Local Educational Agencies, Indian Education - Special Programs for Indian Children, Howard University, Helen Keller National Center for Youths and Adults Who Are Deaf-Blind, Grants for State Assessments and Related Activities, Graduate Assistance in Areas of National Need, Gaining Early Awareness and Readiness for Undergraduate Programs, English Language Acquisition State Grants, Education Research, Development and Dissemination, Education Innovation and Research (formerly Investing in Innovation (i3) Fund), Education for Homeless Children and Youth, Disaster Recovery Assistance for Education, DC Opportunity Scholarship Program, Credit Programs, Credit Enhancement for Charter School Facilities, Consolidated Grant to the Outlying Areas, Comprehensive Literacy Development, Comprehensive Centers, Child Care Access Means Parents in School, Charter Schools, Career and Technical Education - Grants to Native Americans and Alaska Natives, Career and Technical Education - Basic Grants to States, Arts in Education, American Printing House for the Blind, American History and Civics Education, Alaska Native Educational Programs, Adult Education - Basic Grants to States</t>
   </si>
   <si>
@@ -1104,9 +1098,6 @@
   </si>
   <si>
     <t>Payroll</t>
-  </si>
-  <si>
-    <t>Worldwide Security Protection, Working Capital Fund Programs, Voluntary Contributions, Temporary Duty Travel, Security - Afghanistan, Pakistan, Project Construction - Major Rehabilitation, Post-Assignment Travel, Population Refugees and Migration Programs, Peace-Keeping Operations Programs, Overseas Programs, National Endowment for Democracy, Leaseholds and Functional Programs, International Security Programs, International Security and Nonproliferation Related Programs, International Cooperative Administrative Support Services, Fulbright Program, Foreign Service Annuities, Foreign Locally Employed Staff Compensation, Embassy Operations Programs, Educational Programs, Economic Support Fund, Diplomatic Programs, Terrorism Related, Diplomatic Programs, Other Operations Programs, Diplomatic Programs, Diplomatic Policy and Support, Diplomatic Programs, Diplomatic and Support Programs, Consular Information Technology and Security, Consular and Border Security Programs, Construction, Citizens Exchange Program, Capital and Real Property Acquisitions Programs, Aviation, Anticrime, Interdiction and Related Programs, Assessed Contributions, American Compensation</t>
   </si>
   <si>
     <t>Rail Carriers</t>
@@ -1472,9 +1463,6 @@
   </si>
   <si>
     <t>Office of Workers' Compensation - Federal Employees' Compensation Act, Employment &amp; Training Administration - Federal State Unemployment Insurance</t>
-  </si>
-  <si>
-    <t>Travel Pay Navy – Defense Travel System (DTS), Travel Pay Department of Air Force (DAF) - Reserve Travel System (RTS), Travel Pay Army – Defense Travel System (DTS), Military Pay Army – National Guard, Military Health Benefits – TRICARE West Region Program (West), Military Health Benefits – TRICARE Medicare Eligible Program (TMEP), Military Health Benefits – TRICARE East Region Program (East), Commercial Pay – Navy Enterprise and Resource Planning (NERP), Civilian Pay – Other Defense Organization (ODO), Civilian Pay – Army</t>
   </si>
   <si>
     <t>Help America Vote College Program, Help America Vote Act Requirements Payments, Election Security Grants</t>
@@ -2900,6 +2888,18 @@
 If the debt remains unpaid, it is referred to Treasury (within 180 days) for offset via the government-wide TOP and for direct collection action by Treasury and Treasury contracted private collection agencies. Treasury also initiates referral to the Department of Justice (DOJ) for civil litigation and/or initiates Administrative Wage Garnishment (AWG) action if they deem such action to be appropriate. If Treasury’s Cross-Servicing action is not successful, Treasury “returns” the debt to the FOC. If older than two years, the receivable is written-off and the case is reclassified “currently not collectible.” The FOC keeps the case open if offset via TOP appears fruitful or if other collection measures are applicable (e.g., AWG action by HUD). Otherwise, the FOC terminates collection action, closes the case, and the system issues an IRS Form 1099C “Cancellation of Debt,” the following January if appropriate. Write-off, Termination, close-out, and 1099C issuance can also occur at any point in the above collection cycle if determined appropriate (e.g., debtor is discharged as bankrupt). Collections from debtors to HUD go to the Treasury Lockbox Network or Pay.gov. Collections from debtors to Treasury or DOJ come to HUD via interagency transfer (i.e., Intra-Governmental Payment and Collection (IPAC)). No matter the route, all payments are posted to the receivable in DCAMS. "
 Multifamily Insurance Claims
 The Office of Housing-Federal Housing Administration’s (HSNG–FHA) recovery audit program is part of its overall program of effective internal control over payments. Internal control policies and procedures establishes a system to monitor improper payments and their causes, and includes controls and actions for detecting, preventing, and recovering improper payments. On a recurring basis, these programs generate reports that identify potentially duplicate disbursements. These disbursements are researched, and recovery actions are initiated for payments deemed improper. As part of the recapture audit plan, internal control documents and files are reviewed, and post claim reviews are performed. Under Title I and Other Debt Collection Guidance Handbook 4740.2, the Financial Operation Center (FOC) is primarily responsible for generic debt collection and customer service activities, including responding to debtor inquiries regarding pay-off, payment plans, compromises, disputes, and appeals. The debt referral package primarily consists of copies of legal documents, mortgages, deeds of trust, judgments and other recorded lien documents, lien assignment documents, repayment agreements, credit reports, correspondence to/from debtors, and compromise agreements and supporting documents. The Debt Collection Asset Management System (DCAMS) is the application used to support the generic debt collection process. DCAMS is designed to automatically send collection letters, report delinquent debt to credit bureaus and HUD’s Credit Alert Interactive Voice Response System (CAIVRS), assess penalties and administrative costs, and refer eligible debts to the Treasury Offset Program (TOP) and Cross-Servicing. Based on predefined criteria and the status of that case as reflected in DCAMS data fields (not later than 180 days after the demand letter), DCAMS is consistently updated to prevent improper referral for TOP offset. For internal offsets, over-claimed amounts (negative claims) occur when the mortgagee owes FHA. The Single-Family Claims Branch (SFCB) sends billing letters to lenders for the excess amounts claimed and tracks the receivables using the Accounts Receivables Sub-system (ARS). Receivables are established in SFCB’s ARS and identified by an FHA case number. Each FHA case number is further identified by Section of the Act (which is linked to the appropriate fund) and endorsement date. This later date identifies the cohort year. The Holder of record to which the claim funds were originally disbursed is identified in ARS as the debtor, by default. When the receivable is subsequently liquidated by funds remitted by a Mortgagee or by offset, the collected amount is posted to the previously identified FHA case number, Section of the Act, and cohort year. If a payment is not received from a lender within 90 days, the receivable is offset against subsequent claims by the lender until the full amount of the receivable is satisfied. If a receivable is not satisfied within 120-150 days, it is referred to the FOC in Albany, NY for enforced collection actions. At that time, the FOC officially confirms acceptance of the transfer of an aged delinquent debt, and that receivables have been removed from the ARS with the notation that it has been referred to the FOC for recovery. Another avenue by which improper payments are recaptured is through Post Claim Reviews for title II Single Family Insurance Claims. A statistical sample of settled claims is reviewed for compliance with FHA servicing and claim filing requirements. A report on findings, is prepared and issued to the individual mortgagee. Mortgagees can refute the findings by providing additional documents before a final report is issued. If the Mortgagee chooses to pay the monetary findings prior to HUD’s issuance of the final report, those funds are deposited to ARS, which applies them to the Mortgage Insurance (MI) fund. Upon issuance of the final report, it is referred to the FOC which establishes it as a receivable and tracks it until paid in full. If a lender is overpaid on a Multifamily claim, the Multifamily Claims Branch will demand the overage back from the lender. If the lender fails to respond to their demands, the debt is referred to the FOC for collection. Lastly, for Treasury Cross-Servicing, the collection of generic debt is governed by the Debt Collection Improvement Act and HUD policies (Title I and Other Debt Collection Guidance 4740.2). The Act requires federal agencies to refer eligible delinquent debts to Treasury (for Cross-Servicing and TOP) when the debt is 120 days delinquent. The Treasury’s TOP allows federal agencies to report delinquent non-tax debt to the BFS. BFS performs computer matching with disbursement data and processes an offset when an appropriate match is determined. After referral, Treasury and its private collection agencies are responsible for contacting the debtor to collect the payment of the debt. The Treasury’s Cross-Servicing is a process used by BFS to refer the debt collection to a private....</t>
+  </si>
+  <si>
+    <t>Worldwide Security Protection, Working Capital Fund Programs, Voluntary Contributions, Temporary Duty Travel, Security - Afghanistan, Pakistan, Project Construction - Major Rehabilitation, Post-Assignment Travel, Population Refugees and Migration Programs, Peace-Keeping Operations Programs, Overseas Programs, National Endowment for Democracy, Leaseholds and Functional Programs, International Security Programs, International Security and Nonproliferation Related Programs, International Cooperative Administrative Support Services, Fulbright Program, Foreign Service Annuities, Foreign Locally Employed Staff Compensation, Embassy Operations Programs, Educational Programs, Economic Support Fund, Diplomatic Programs, Terrorism Related, Other Operations Programs, Diplomatic Programs, Diplomatic Policy and Support, Diplomatic Programs, Diplomatic and Support Programs, Consular Information Technology and Security, Consular and Border Security Programs, Construction, Citizens Exchange Program, Capital and Real Property Acquisitions Programs, Aviation, Anticrime, Interdiction and Related Programs, Assessed Contributions, American Compensation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel Pay Navy – Defense Travel System (DTS), Travel Pay Department of Air Force (DAF) - Defense Travel System (DTS), Travel Pay Army – Defense Travel System (DTS), Military Pay Army – National Guard, Military Health Benefits – TRICARE West Region Program (West), Military Health Benefits – TRICARE Medicare Eligible Program (TMEP), Military Health Benefits – TRICARE East Region Program (East), Civilian Pay – Other Defense Organization (ODO), Civilian Pay – Army, Commercial Pay – Mechanization of Contract Administration Services (MOCAS), </t>
+  </si>
+  <si>
+    <t>Travel Pay Marine Corps – Integrated Automated Travel System (IATS), Military Retirement – Retired Pay, Military Retirement – Combat Related Special Compensation, Military Retirement – Annuitant Pay, Military Pay Department of Air Force (DAF) – Reserve, Military Pay Department of Air Force (DAF) – Air National Guard, Military Pay Department of Air Force (DAF) – Active Duty, Military Pay Army – Reserve, Military Pay Army – Active Duty, Commercial Pay – Transportation Financial Management System (TFMS), Commercial Pay – Standard Automated Voucher Examination System (SAVES), Commercial Pay – ONEPAY, Commercial Pay – Mechanization of Contract Administration Services (MOCAS), Commercial Pay – Integrated Accounts Payable System (IAPS), Commercial Pay – General Fund Enterprise Business System (GFEBS), Commercial Pay – Financial Accounting and Budgetary System (FABS), Commercial Pay – Enterprise Business System (EBS), Civilian Pay – Department of Air Force (DAF), Commercial Pay – Navy Enterprise and Resource Planning (NERP), Commercial Pay – Defense Enterprise Accounting Management System (DEAMS)</t>
+  </si>
+  <si>
+    <t>Veterans Employment Training Service - Federal Administration &amp; Uniformed Services Employment and Reemployment Rights Act (USERRA) Enforcement, Office of Workers' Compensation - Coal Mine Workers' Compensation, Office of Workers' Compensation - Longshore and Harbor Workers Compensation, Office of Labor-Management Standards, Mine Safety and Health Administration, Employment &amp; Training Administration - Work Opportunity Tax Credit Program (WOTC), Employment &amp; Training Administration - WIOA National Dislocated Worker Grants / WIA National Emergency Grants, Employment &amp; Training Administration - WIOA Dislocated Worker National Reserve Technical Assistance and Training, Employment &amp; Training Administration - Trade Adjustment Assistance Federal Unemployment Benefits and Allowances, Employment &amp; Training Administration - Temporary Labor Certification for Foreign Workers, Employment &amp; Training Administration - Permanent Labor Certification for Foreign Workers, Employment &amp; Training Administration - Job Corps, Employment &amp; Training Administration - Indian and Native American Program, Employment &amp; Training Administration - H-1B Job Training Grants, Employment &amp; Training Administration - Employment Service, Employment &amp; Training Administration - Dislocated Worker Employment and Training Activities - National Reserves Demos, Employment &amp; Training Administration - Community Projects, Bureau of Labor Statistics - Labor Force Statistics, Bureau of Labor Statistics - Compensation and Working Conditions</t>
   </si>
 </sst>
 </file>
@@ -3367,14 +3367,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AQ200"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="27.3984375" customWidth="1"/>
-    <col min="5" max="5" width="17.265625" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="D1" s="2" t="s">
         <v>65</v>
       </c>
@@ -3432,7 +3432,7 @@
       <c r="AP1" s="15"/>
       <c r="AQ1" s="15"/>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="D2" s="2" t="s">
         <v>64</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>108</v>
       </c>
       <c r="X2" s="9" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="Y2" s="2" t="s">
         <v>110</v>
@@ -3530,13 +3530,13 @@
         <v>130</v>
       </c>
       <c r="AJ2" s="13" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="AK2" s="13" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="AL2" s="13" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="AM2" s="2" t="s">
         <v>132</v>
@@ -3554,9 +3554,9 @@
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:43" s="6" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:43" s="6" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>143</v>
@@ -3625,7 +3625,7 @@
         <v>107</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="Y3" s="5" t="s">
         <v>109</v>
@@ -3661,13 +3661,13 @@
         <v>129</v>
       </c>
       <c r="AJ3" s="5" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="AK3" s="5" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="AM3" s="5" t="s">
         <v>131</v>
@@ -3685,9 +3685,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>0</v>
@@ -3714,11 +3714,11 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="S4" s="7">
         <v>0</v>
@@ -3727,13 +3727,13 @@
         <v>0</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="Z4" s="7">
         <v>0</v>
@@ -3753,28 +3753,28 @@
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
       <c r="AN4" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO4" s="3" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="AP4" s="3" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="AQ4" s="3" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.45">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>1</v>
@@ -3796,35 +3796,35 @@
         <v>265</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="X5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="Z5" s="7"/>
       <c r="AA5" s="7">
@@ -3847,21 +3847,21 @@
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
       <c r="AN5" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO5" s="3" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AP5" s="3" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="AQ5" s="3" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.45">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
@@ -3883,30 +3883,30 @@
         <v>266</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="S6" s="7">
         <v>0.9</v>
@@ -3915,15 +3915,15 @@
         <v>0.8</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="X6" s="3"/>
       <c r="Y6" s="3" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7">
@@ -3946,21 +3946,21 @@
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
       <c r="AN6" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO6" s="3" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AP6" s="3" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="AQ6" s="3" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.45">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
@@ -3982,35 +3982,35 @@
         <v>267</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q7" s="3"/>
       <c r="R7" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
       <c r="U7" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="X7" s="3"/>
       <c r="Y7" s="3" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="Z7" s="7"/>
       <c r="AA7" s="7">
@@ -4033,21 +4033,21 @@
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO7" s="3" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="AP7" s="3" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="AQ7" s="3" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.45">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>4</v>
@@ -4076,24 +4076,24 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="X8" s="3"/>
       <c r="Y8" s="3" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="Z8" s="7"/>
       <c r="AA8" s="7">
@@ -4116,21 +4116,21 @@
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
       <c r="AN8" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO8" s="3" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AP8" s="3" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="AQ8" s="3" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.45">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -4152,33 +4152,33 @@
         <v>268</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="U9" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="Z9" s="7"/>
       <c r="AA9" s="7">
@@ -4201,21 +4201,21 @@
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
       <c r="AN9" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO9" s="3" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AP9" s="3" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="AQ9" s="3" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.45">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
@@ -4239,22 +4239,22 @@
         <v>269</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="S10" s="7">
         <v>45.731999999999999</v>
@@ -4263,15 +4263,15 @@
         <v>102.172</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="Z10" s="7"/>
       <c r="AA10" s="7">
@@ -4294,21 +4294,21 @@
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
       <c r="AN10" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO10" s="3" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="AP10" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="AQ10" s="3" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.45">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -4337,22 +4337,22 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="Z11" s="7"/>
       <c r="AA11" s="7">
@@ -4375,21 +4375,21 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO11" s="3" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="AP11" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AQ11" s="3" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.45">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>8</v>
@@ -4411,22 +4411,22 @@
         <v>270</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="S12" s="7">
         <v>51.7</v>
@@ -4435,15 +4435,15 @@
         <v>51</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="X12" s="3"/>
       <c r="Y12" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="Z12" s="7"/>
       <c r="AA12" s="7">
@@ -4466,21 +4466,21 @@
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
       <c r="AN12" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO12" s="3" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="AP12" s="3" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="AQ12" s="3" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.45">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>9</v>
@@ -4504,22 +4504,22 @@
         <v>271</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q13" s="3"/>
       <c r="R13" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="S13" s="7">
         <v>69.17</v>
@@ -4528,15 +4528,15 @@
         <v>65.12</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="Z13" s="7"/>
       <c r="AA13" s="7">
@@ -4559,21 +4559,21 @@
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
       <c r="AN13" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="AP13" s="3" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="AQ13" s="3" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.45">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>10</v>
@@ -4595,22 +4595,22 @@
         <v>272</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="S14" s="7">
         <v>9.56</v>
@@ -4619,15 +4619,15 @@
         <v>10.35</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="X14" s="3"/>
       <c r="Y14" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7">
@@ -4650,21 +4650,21 @@
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
       <c r="AN14" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO14" s="3" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="AP14" s="3" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="AQ14" s="3" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.45">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>11</v>
@@ -4688,22 +4688,22 @@
         <v>273</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="S15" s="7">
         <v>4.28</v>
@@ -4712,13 +4712,13 @@
         <v>4.07</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="Z15" s="7">
         <v>0.19</v>
@@ -4748,30 +4748,30 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="AN15" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO15" s="3" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="AP15" s="3" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AQ15" s="3" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.45">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>12</v>
@@ -4792,33 +4792,33 @@
         <v>238</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>274</v>
+        <v>781</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="S16" s="7">
         <v>0</v>
@@ -4827,17 +4827,17 @@
         <v>0</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="X16" s="3"/>
       <c r="Y16" s="3" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="Z16" s="7">
         <v>1841.39</v>
@@ -4867,30 +4867,30 @@
         <v>942.99</v>
       </c>
       <c r="AI16" s="3" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="AN16" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO16" s="3" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="AP16" s="3" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="AQ16" s="3" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.45">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>13</v>
@@ -4911,25 +4911,25 @@
         <v>238</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="S17" s="7">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="Z17" s="7">
         <v>22.51096188</v>
@@ -4974,30 +4974,30 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
       <c r="AM17" s="3" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="AN17" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO17" s="3" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="AP17" s="3" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="AQ17" s="3" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.45">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>14</v>
@@ -5016,48 +5016,48 @@
         <v>238</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>276</v>
+        <v>780</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>318</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>396</v>
+        <v>779</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
       <c r="U18" s="3" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="Z18" s="7">
         <v>1369.46</v>
@@ -5087,30 +5087,30 @@
         <v>92.29</v>
       </c>
       <c r="AI18" s="3" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
       <c r="AM18" s="3" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AN18" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO18" s="3" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="AP18" s="3" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="AQ18" s="3" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.45">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>15</v>
@@ -5134,33 +5134,33 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="Z19" s="7"/>
       <c r="AA19" s="7">
@@ -5183,21 +5183,21 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO19" s="3" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="AP19" s="3" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="AQ19" s="3" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.45">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>16</v>
@@ -5216,25 +5216,25 @@
         <v>240</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="S20" s="7">
         <v>443.54</v>
@@ -5243,15 +5243,15 @@
         <v>430.79</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="X20" s="3"/>
       <c r="Y20" s="3" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="Z20" s="7"/>
       <c r="AA20" s="7">
@@ -5274,21 +5274,21 @@
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
       <c r="AN20" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO20" s="3" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="AP20" s="3" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="AQ20" s="3" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.45">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>17</v>
@@ -5307,25 +5307,25 @@
         <v>240</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="S21" s="7">
         <v>0</v>
@@ -5334,15 +5334,15 @@
         <v>0</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="X21" s="3"/>
       <c r="Y21" s="3" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="Z21" s="7"/>
       <c r="AA21" s="7">
@@ -5365,21 +5365,21 @@
       <c r="AL21" s="3"/>
       <c r="AM21" s="3"/>
       <c r="AN21" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO21" s="3" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="AP21" s="3" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="AQ21" s="3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.45">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>18</v>
@@ -5400,33 +5400,33 @@
         <v>240</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="S22" s="7">
         <v>50.47</v>
@@ -5435,15 +5435,15 @@
         <v>55.95</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="X22" s="3"/>
       <c r="Y22" s="3" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="Z22" s="7"/>
       <c r="AA22" s="7">
@@ -5466,21 +5466,21 @@
       <c r="AL22" s="3"/>
       <c r="AM22" s="3"/>
       <c r="AN22" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO22" s="3" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="AP22" s="3" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="AQ22" s="3" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.45">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>19</v>
@@ -5507,24 +5507,24 @@
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="3" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="3" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="X23" s="3"/>
       <c r="Y23" s="3" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="Z23" s="7"/>
       <c r="AA23" s="7">
@@ -5547,17 +5547,17 @@
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
       <c r="AN23" s="3" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
       <c r="AQ23" s="3" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.45">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>20</v>
@@ -5586,11 +5586,11 @@
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="S24" s="7">
         <v>5.0999999999999997E-2</v>
@@ -5599,13 +5599,13 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="Z24" s="7"/>
       <c r="AA24" s="7">
@@ -5628,17 +5628,17 @@
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
       <c r="AN24" s="3" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
       <c r="AQ24" s="3" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.45">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>21</v>
@@ -5659,35 +5659,35 @@
         <v>242</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="S25" s="7">
         <v>30.43</v>
@@ -5696,15 +5696,15 @@
         <v>20.89</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="Z25" s="7">
         <v>3.72</v>
@@ -5734,30 +5734,30 @@
         <v>0.02</v>
       </c>
       <c r="AI25" s="3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
       <c r="AM25" s="3" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AN25" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AO25" s="3" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="AP25" s="3" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="AQ25" s="3" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.45">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>22</v>
@@ -5784,24 +5784,24 @@
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="3" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="X26" s="3"/>
       <c r="Y26" s="3" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="Z26" s="7"/>
       <c r="AA26" s="7">
@@ -5824,21 +5824,21 @@
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
       <c r="AN26" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AO26" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="AP26" s="3" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="AQ26" s="3" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.45">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>23</v>
@@ -5857,38 +5857,38 @@
         <v>244</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="Q27" s="3"/>
       <c r="R27" s="3" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="X27" s="3"/>
       <c r="Y27" s="3" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="Z27" s="7">
         <v>0</v>
@@ -5908,28 +5908,28 @@
       <c r="AG27" s="3"/>
       <c r="AH27" s="3"/>
       <c r="AI27" s="3" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
       <c r="AM27" s="3"/>
       <c r="AN27" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AO27" s="3" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AP27" s="3" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="AQ27" s="3" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.45">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>24</v>
@@ -5950,25 +5950,25 @@
         <v>244</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="S28" s="7">
         <v>0</v>
@@ -5977,13 +5977,13 @@
         <v>0</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="Z28" s="7">
         <v>3.9E-2</v>
@@ -6013,30 +6013,30 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
       <c r="AM28" s="3" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AN28" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AO28" s="3" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AP28" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="AQ28" s="3" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.45">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>25</v>
@@ -6065,24 +6065,24 @@
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
       <c r="U29" s="3" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="X29" s="3"/>
       <c r="Y29" s="3" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="Z29" s="7"/>
       <c r="AA29" s="7">
@@ -6105,21 +6105,21 @@
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
       <c r="AN29" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AO29" s="3" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AP29" s="3" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="AQ29" s="3" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.45">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>26</v>
@@ -6140,25 +6140,25 @@
         <v>246</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="S30" s="7">
         <v>6.0979999999999999E-2</v>
@@ -6167,13 +6167,13 @@
         <v>6.0979999999999999E-2</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="Z30" s="7">
         <v>8.9999999999999998E-4</v>
@@ -6203,30 +6203,30 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
       <c r="AM30" s="3" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="AN30" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AO30" s="3" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AP30" s="3" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="AQ30" s="3" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.45">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>27</v>
@@ -6245,25 +6245,25 @@
         <v>246</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="S31" s="7">
         <v>13.16</v>
@@ -6272,13 +6272,13 @@
         <v>16.28</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="Z31" s="7">
         <v>2.17</v>
@@ -6308,30 +6308,30 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
       <c r="AM31" s="3" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="AN31" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AO31" s="3" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AP31" s="3" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="AQ31" s="3" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.45">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>28</v>
@@ -6352,33 +6352,33 @@
         <v>246</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="S32" s="7">
         <v>17142.009999999998</v>
@@ -6387,15 +6387,15 @@
         <v>13397.37</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="X32" s="3"/>
       <c r="Y32" s="3" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="Z32" s="7">
         <v>991.05</v>
@@ -6425,30 +6425,30 @@
         <v>84.13</v>
       </c>
       <c r="AI32" s="3" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
       <c r="AM32" s="3" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="AN32" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AO32" s="3" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AP32" s="3" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="AQ32" s="3" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="33" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.45">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="33" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>29</v>
@@ -6467,33 +6467,33 @@
         <v>246</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="S33" s="7">
         <v>17.059999999999999</v>
@@ -6502,19 +6502,19 @@
         <v>23.08</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="W33" s="12" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="X33" s="12" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="Z33" s="7">
         <v>7.75</v>
@@ -6544,32 +6544,32 @@
         <v>0</v>
       </c>
       <c r="AI33" s="14" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="AJ33" s="14" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="AK33" s="14" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="AL33" s="14" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="AM33" s="3" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AN33" s="3" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="AO33" s="3"/>
       <c r="AP33" s="3"/>
       <c r="AQ33" s="3" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.45">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>30</v>
@@ -6588,38 +6588,38 @@
         <v>246</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q34" s="3"/>
       <c r="R34" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="12" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="X34" s="3"/>
       <c r="Y34" s="3" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="Z34" s="7"/>
       <c r="AA34" s="7">
@@ -6642,21 +6642,21 @@
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
       <c r="AN34" s="3" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="AO34" s="3" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="AP34" s="3" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="AQ34" s="3" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.45">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>31</v>
@@ -6685,11 +6685,11 @@
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q35" s="3"/>
       <c r="R35" s="3" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="S35" s="7">
         <v>3.34</v>
@@ -6698,15 +6698,15 @@
         <v>0.01</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="12" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="X35" s="3"/>
       <c r="Y35" s="3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="Z35" s="7"/>
       <c r="AA35" s="7">
@@ -6729,21 +6729,21 @@
       <c r="AL35" s="3"/>
       <c r="AM35" s="3"/>
       <c r="AN35" s="3" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="AO35" s="3" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="AP35" s="3" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="AQ35" s="3" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.45">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>32</v>
@@ -6762,38 +6762,38 @@
         <v>248</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q36" s="3"/>
       <c r="R36" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="12" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="Z36" s="7">
         <v>0</v>
@@ -6813,28 +6813,28 @@
       <c r="AG36" s="3"/>
       <c r="AH36" s="3"/>
       <c r="AI36" s="3" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
       <c r="AM36" s="3"/>
       <c r="AN36" s="3" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="AO36" s="3" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="AP36" s="3" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="AQ36" s="3" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.45">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>33</v>
@@ -6853,38 +6853,38 @@
         <v>248</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="12" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="X37" s="3"/>
       <c r="Y37" s="3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="Z37" s="7"/>
       <c r="AA37" s="7">
@@ -6907,17 +6907,17 @@
       <c r="AL37" s="3"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="AO37" s="3"/>
       <c r="AP37" s="3"/>
       <c r="AQ37" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.45">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>34</v>
@@ -6944,11 +6944,11 @@
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="S38" s="7">
         <v>0.27100000000000002</v>
@@ -6957,15 +6957,15 @@
         <v>0.217</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="12" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="X38" s="3"/>
       <c r="Y38" s="3" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7">
@@ -6988,21 +6988,21 @@
       <c r="AL38" s="3"/>
       <c r="AM38" s="3"/>
       <c r="AN38" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO38" s="3" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="AP38" s="3" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="AQ38" s="3" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.45">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>35</v>
@@ -7021,25 +7021,25 @@
         <v>250</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q39" s="3"/>
       <c r="R39" s="3" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="S39" s="7">
         <v>15.56</v>
@@ -7048,15 +7048,15 @@
         <v>11.64</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="12" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="X39" s="3"/>
       <c r="Y39" s="3" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="Z39" s="7"/>
       <c r="AA39" s="7">
@@ -7079,21 +7079,21 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO39" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AP39" s="3" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="AQ39" s="3" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.45">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>36</v>
@@ -7120,24 +7120,24 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q40" s="3"/>
       <c r="R40" s="3" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="12" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="X40" s="3"/>
       <c r="Y40" s="3" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="Z40" s="7"/>
       <c r="AA40" s="7">
@@ -7160,21 +7160,21 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AP40" s="3" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="AQ40" s="3" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.45">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>37</v>
@@ -7193,25 +7193,25 @@
         <v>252</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="S41" s="7">
         <v>0</v>
@@ -7220,13 +7220,13 @@
         <v>0</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="11"/>
       <c r="X41" s="3"/>
       <c r="Y41" s="3" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="Z41" s="7"/>
       <c r="AA41" s="7">
@@ -7249,21 +7249,21 @@
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
       <c r="AN41" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO41" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AP41" s="3" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="AQ41" s="3" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.45">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>38</v>
@@ -7282,38 +7282,38 @@
         <v>252</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q42" s="3"/>
       <c r="R42" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="12" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="X42" s="3"/>
       <c r="Y42" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="Z42" s="7"/>
       <c r="AA42" s="7">
@@ -7336,21 +7336,21 @@
       <c r="AL42" s="3"/>
       <c r="AM42" s="3"/>
       <c r="AN42" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO42" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AP42" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="AQ42" s="3" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.45">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>39</v>
@@ -7369,38 +7369,38 @@
         <v>252</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q43" s="3"/>
       <c r="R43" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="12" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="X43" s="3"/>
       <c r="Y43" s="3" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="Z43" s="7"/>
       <c r="AA43" s="7">
@@ -7423,21 +7423,21 @@
       <c r="AL43" s="3"/>
       <c r="AM43" s="3"/>
       <c r="AN43" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO43" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AP43" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="AQ43" s="3" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.45">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>40</v>
@@ -7466,24 +7466,24 @@
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q44" s="3"/>
       <c r="R44" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="12" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="X44" s="3"/>
       <c r="Y44" s="3" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="Z44" s="7"/>
       <c r="AA44" s="7">
@@ -7506,21 +7506,21 @@
       <c r="AL44" s="3"/>
       <c r="AM44" s="3"/>
       <c r="AN44" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO44" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AP44" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="AQ44" s="3" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.45">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>41</v>
@@ -7547,11 +7547,11 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="S45" s="7">
         <v>16.010000000000002</v>
@@ -7560,15 +7560,15 @@
         <v>16.010000000000002</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="12" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="X45" s="3"/>
       <c r="Y45" s="3" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="Z45" s="7"/>
       <c r="AA45" s="7">
@@ -7591,21 +7591,21 @@
       <c r="AL45" s="3"/>
       <c r="AM45" s="3"/>
       <c r="AN45" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO45" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AP45" s="3" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AQ45" s="3" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.45">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>42</v>
@@ -7626,38 +7626,38 @@
         <v>254</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q46" s="3"/>
       <c r="R46" s="3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
       <c r="U46" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="12" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="X46" s="3"/>
       <c r="Y46" s="3" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="Z46" s="7"/>
       <c r="AA46" s="7">
@@ -7680,21 +7680,21 @@
       <c r="AL46" s="3"/>
       <c r="AM46" s="3"/>
       <c r="AN46" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO46" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AP46" s="3" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AQ46" s="3" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.45">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>43</v>
@@ -7718,22 +7718,22 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="S47" s="7">
         <v>321.75</v>
@@ -7742,15 +7742,15 @@
         <v>245.14</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="12" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="X47" s="3"/>
       <c r="Y47" s="3" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="Z47" s="7"/>
       <c r="AA47" s="7">
@@ -7773,21 +7773,21 @@
       <c r="AL47" s="3"/>
       <c r="AM47" s="3"/>
       <c r="AN47" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO47" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AP47" s="3" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AQ47" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.45">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>44</v>
@@ -7814,24 +7814,24 @@
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
       <c r="P48" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="Q48" s="3"/>
       <c r="R48" s="3" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="12" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="X48" s="3"/>
       <c r="Y48" s="3" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="Z48" s="7"/>
       <c r="AA48" s="7">
@@ -7854,21 +7854,21 @@
       <c r="AL48" s="3"/>
       <c r="AM48" s="3"/>
       <c r="AN48" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO48" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AP48" s="3" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="AQ48" s="3" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.45">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>45</v>
@@ -7887,25 +7887,25 @@
         <v>256</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="Q49" s="3"/>
       <c r="R49" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="S49" s="7">
         <v>11.9</v>
@@ -7914,15 +7914,15 @@
         <v>11.9</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="12" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="X49" s="3"/>
       <c r="Y49" s="3" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="Z49" s="7"/>
       <c r="AA49" s="7">
@@ -7945,21 +7945,21 @@
       <c r="AL49" s="3"/>
       <c r="AM49" s="3"/>
       <c r="AN49" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO49" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AP49" s="3" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="AQ49" s="3" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.45">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>46</v>
@@ -7986,11 +7986,11 @@
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
       <c r="P50" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="Q50" s="3"/>
       <c r="R50" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="S50" s="7">
         <v>9.5000000000000001E-2</v>
@@ -7999,15 +7999,15 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="12" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="X50" s="3"/>
       <c r="Y50" s="3" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="Z50" s="7"/>
       <c r="AA50" s="7">
@@ -8030,21 +8030,21 @@
       <c r="AL50" s="3"/>
       <c r="AM50" s="3"/>
       <c r="AN50" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO50" s="3" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AP50" s="3" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AQ50" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.45">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>47</v>
@@ -8063,25 +8063,25 @@
         <v>258</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
       <c r="P51" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="S51" s="7">
         <v>0</v>
@@ -8090,13 +8090,13 @@
         <v>0</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="11"/>
       <c r="X51" s="3"/>
       <c r="Y51" s="3" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="Z51" s="7">
         <v>0</v>
@@ -8116,28 +8116,28 @@
       <c r="AG51" s="3"/>
       <c r="AH51" s="3"/>
       <c r="AI51" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="AJ51" s="3"/>
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
       <c r="AM51" s="3"/>
       <c r="AN51" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO51" s="3" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AP51" s="3" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AQ51" s="3" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.45">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>48</v>
@@ -8166,24 +8166,24 @@
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="Q52" s="3"/>
       <c r="R52" s="3" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
       <c r="U52" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="12" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="3" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="Z52" s="7"/>
       <c r="AA52" s="7">
@@ -8206,21 +8206,21 @@
       <c r="AL52" s="3"/>
       <c r="AM52" s="3"/>
       <c r="AN52" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO52" s="3" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AP52" s="3" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AQ52" s="3" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.45">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
@@ -8239,25 +8239,25 @@
         <v>260</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
       <c r="P53" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="S53" s="7">
         <v>94.5</v>
@@ -8266,15 +8266,15 @@
         <v>81</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="12" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="3" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="Z53" s="7"/>
       <c r="AA53" s="7">
@@ -8297,21 +8297,21 @@
       <c r="AL53" s="3"/>
       <c r="AM53" s="3"/>
       <c r="AN53" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO53" s="3" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AP53" s="3" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="AQ53" s="3" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.45">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>50</v>
@@ -8337,22 +8337,22 @@
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="S54" s="7">
         <v>616.17999999999995</v>
@@ -8361,15 +8361,15 @@
         <v>3.81</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="12" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="3" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="Z54" s="7"/>
       <c r="AA54" s="7">
@@ -8392,21 +8392,21 @@
       <c r="AL54" s="3"/>
       <c r="AM54" s="3"/>
       <c r="AN54" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO54" s="3" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AP54" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="AQ54" s="3" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.45">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>51</v>
@@ -8427,38 +8427,38 @@
         <v>262</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="12" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="X55" s="3"/>
       <c r="Y55" s="3" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="Z55" s="7"/>
       <c r="AA55" s="7">
@@ -8481,21 +8481,21 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO55" s="3" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AP55" s="3" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="AQ55" s="3" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.45">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>52</v>
@@ -8507,7 +8507,7 @@
         <v>165</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="F56" s="7">
         <v>143.24794900000001</v>
@@ -8516,35 +8516,35 @@
         <v>262</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="S56" s="7">
         <v>10860</v>
@@ -8553,13 +8553,13 @@
         <v>4925</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="11"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="Z56" s="7"/>
       <c r="AA56" s="7">
@@ -8582,21 +8582,21 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO56" s="3" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AP56" s="3" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="AQ56" s="3" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.45">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>53</v>
@@ -8617,33 +8617,33 @@
         <v>262</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L57" s="3"/>
       <c r="M57" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="S57" s="7">
         <v>0.01</v>
@@ -8652,15 +8652,15 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="12" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="X57" s="3"/>
       <c r="Y57" s="3" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="Z57" s="7"/>
       <c r="AA57" s="7">
@@ -8683,21 +8683,21 @@
       <c r="AL57" s="3"/>
       <c r="AM57" s="3"/>
       <c r="AN57" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO57" s="3" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AP57" s="3" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="AQ57" s="3" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.45">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>54</v>
@@ -8718,25 +8718,25 @@
         <v>262</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>301</v>
+        <v>778</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
       <c r="P58" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="Q58" s="3"/>
       <c r="R58" s="3" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="S58" s="7">
         <v>32.07998542</v>
@@ -8745,15 +8745,15 @@
         <v>32.77794085</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="12" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="X58" s="3"/>
       <c r="Y58" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="Z58" s="7">
         <v>7.9287300000000002E-3</v>
@@ -8783,30 +8783,30 @@
         <v>0</v>
       </c>
       <c r="AI58" s="3" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="AJ58" s="3"/>
       <c r="AK58" s="3"/>
       <c r="AL58" s="3"/>
       <c r="AM58" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="AN58" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AO58" s="3" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AP58" s="3" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AQ58" s="3" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.45">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>55</v>
@@ -8825,38 +8825,38 @@
         <v>262</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
       <c r="P59" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="Q59" s="3"/>
       <c r="R59" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="S59" s="3"/>
       <c r="T59" s="3"/>
       <c r="U59" s="3" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="12" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="X59" s="3"/>
       <c r="Y59" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="Z59" s="7"/>
       <c r="AA59" s="7">
@@ -8879,17 +8879,17 @@
       <c r="AL59" s="3"/>
       <c r="AM59" s="3"/>
       <c r="AN59" s="3" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AO59" s="3"/>
       <c r="AP59" s="3"/>
       <c r="AQ59" s="3" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.45">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>56</v>
@@ -8910,35 +8910,35 @@
         <v>262</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="L60" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>324</v>
-      </c>
       <c r="M60" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="S60" s="7">
         <v>1872.58</v>
@@ -8947,15 +8947,15 @@
         <v>34.49</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="V60" s="3" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="W60" s="11"/>
       <c r="X60" s="3"/>
       <c r="Y60" s="3" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="Z60" s="7">
         <v>5.09</v>
@@ -8985,30 +8985,30 @@
         <v>0.04</v>
       </c>
       <c r="AI60" s="3" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="AJ60" s="3"/>
       <c r="AK60" s="3"/>
       <c r="AL60" s="3"/>
       <c r="AM60" s="3" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="AN60" s="3" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="AO60" s="3" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AP60" s="3" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AQ60" s="3" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.45">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>57</v>
@@ -9029,25 +9029,25 @@
         <v>262</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
       <c r="P61" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="Q61" s="3"/>
       <c r="R61" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="S61" s="7">
         <v>0.52</v>
@@ -9056,15 +9056,15 @@
         <v>0.51</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="12" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="X61" s="3"/>
       <c r="Y61" s="3" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="Z61" s="7">
         <v>0.93</v>
@@ -9094,26 +9094,26 @@
         <v>0.02</v>
       </c>
       <c r="AI61" s="3" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="AJ61" s="3"/>
       <c r="AK61" s="3"/>
       <c r="AL61" s="3"/>
       <c r="AM61" s="3" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="AN61" s="3" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="AO61" s="3"/>
       <c r="AP61" s="3"/>
       <c r="AQ61" s="3" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.45">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>58</v>
@@ -9132,35 +9132,35 @@
         <v>262</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L62" s="3"/>
       <c r="M62" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="S62" s="7">
         <v>652.55999999999995</v>
@@ -9169,15 +9169,15 @@
         <v>458.39</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="12" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="X62" s="3"/>
       <c r="Y62" s="3" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="Z62" s="7"/>
       <c r="AA62" s="7">
@@ -9200,21 +9200,21 @@
       <c r="AL62" s="3"/>
       <c r="AM62" s="3"/>
       <c r="AN62" s="3" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="AO62" s="3" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AP62" s="3" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="AQ62" s="3" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.45">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>59</v>
@@ -9241,11 +9241,11 @@
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
       <c r="P63" s="3" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="Q63" s="3"/>
       <c r="R63" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="S63" s="7">
         <v>0</v>
@@ -9254,13 +9254,13 @@
         <v>0</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="11"/>
       <c r="X63" s="3"/>
       <c r="Y63" s="3" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="Z63" s="7"/>
       <c r="AA63" s="7">
@@ -9283,17 +9283,17 @@
       <c r="AL63" s="3"/>
       <c r="AM63" s="3"/>
       <c r="AN63" s="3" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="AO63" s="3"/>
       <c r="AP63" s="3"/>
       <c r="AQ63" s="3" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.45">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>60</v>
@@ -9320,24 +9320,24 @@
       <c r="N64" s="3"/>
       <c r="O64" s="3"/>
       <c r="P64" s="3" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="Q64" s="3"/>
       <c r="R64" s="3" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="S64" s="3"/>
       <c r="T64" s="3"/>
       <c r="U64" s="3" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="12" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="X64" s="3"/>
       <c r="Y64" s="3" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="Z64" s="7"/>
       <c r="AA64" s="7">
@@ -9360,21 +9360,21 @@
       <c r="AL64" s="3"/>
       <c r="AM64" s="3"/>
       <c r="AN64" s="3" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="AO64" s="3" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AP64" s="3" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="AQ64" s="3" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.45">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>61</v>
@@ -9393,25 +9393,25 @@
         <v>264</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J65" s="3"/>
       <c r="K65" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
       <c r="P65" s="3" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="Q65" s="3"/>
       <c r="R65" s="3" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="S65" s="7">
         <v>0.26</v>
@@ -9420,15 +9420,15 @@
         <v>0.08</v>
       </c>
       <c r="U65" s="3" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="V65" s="3"/>
       <c r="W65" s="12" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="X65" s="3"/>
       <c r="Y65" s="3" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="Z65" s="7"/>
       <c r="AA65" s="7">
@@ -9451,21 +9451,21 @@
       <c r="AL65" s="3"/>
       <c r="AM65" s="3"/>
       <c r="AN65" s="3" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="AO65" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="AP65" s="3" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="AQ65" s="3" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.45">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>62</v>
@@ -9486,33 +9486,33 @@
         <v>264</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L66" s="3"/>
       <c r="M66" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="S66" s="7">
         <v>2079.4299999999998</v>
@@ -9521,13 +9521,13 @@
         <v>970.47</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="V66" s="3"/>
       <c r="W66" s="11"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="3" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="Z66" s="7">
         <v>35.01</v>
@@ -9557,431 +9557,431 @@
         <v>1.26</v>
       </c>
       <c r="AI66" s="3" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AJ66" s="3"/>
       <c r="AK66" s="3"/>
       <c r="AL66" s="3"/>
       <c r="AM66" s="3" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="AN66" s="3" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="AO66" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="AP66" s="3" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="AQ66" s="3" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.45">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W67" s="12" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.45">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W68" s="12" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.45">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W69" s="11"/>
     </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W70" s="12"/>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W71" s="12"/>
     </row>
-    <row r="72" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W72" s="11"/>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W73" s="12"/>
     </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W74" s="12"/>
     </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W75" s="12"/>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W76" s="12"/>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W77" s="12"/>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W78" s="12"/>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W79" s="12"/>
     </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
       <c r="W80" s="11"/>
     </row>
-    <row r="81" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="81" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W81" s="11"/>
     </row>
-    <row r="82" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="82" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W82" s="12"/>
     </row>
-    <row r="83" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="83" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W83" s="12"/>
     </row>
-    <row r="84" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="84" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W84" s="12"/>
     </row>
-    <row r="85" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="85" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W85" s="12"/>
     </row>
-    <row r="86" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="86" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W86" s="12"/>
     </row>
-    <row r="87" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="87" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W87" s="11"/>
     </row>
-    <row r="88" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="88" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W88" s="12"/>
     </row>
-    <row r="89" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="89" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W89" s="12"/>
     </row>
-    <row r="90" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="90" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W90" s="12"/>
     </row>
-    <row r="91" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="91" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W91" s="12"/>
     </row>
-    <row r="92" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="92" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W92" s="12"/>
     </row>
-    <row r="93" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="93" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W93" s="12"/>
     </row>
-    <row r="94" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="94" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W94" s="12"/>
     </row>
-    <row r="95" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="95" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W95" s="11"/>
     </row>
-    <row r="96" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="96" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W96" s="12"/>
     </row>
-    <row r="97" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="97" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W97" s="12"/>
     </row>
-    <row r="98" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="98" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W98" s="12"/>
     </row>
-    <row r="99" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="99" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W99" s="12"/>
     </row>
-    <row r="100" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="100" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W100" s="11"/>
     </row>
-    <row r="101" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="101" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W101" s="12"/>
     </row>
-    <row r="102" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="102" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W102" s="12"/>
     </row>
-    <row r="103" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="103" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W103" s="12"/>
     </row>
-    <row r="104" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="104" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W104" s="12"/>
     </row>
-    <row r="105" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="105" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W105" s="12"/>
     </row>
-    <row r="106" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="106" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W106" s="12"/>
     </row>
-    <row r="107" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="107" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W107" s="11"/>
     </row>
-    <row r="108" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="108" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W108" s="12"/>
     </row>
-    <row r="109" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="109" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W109" s="12"/>
     </row>
-    <row r="110" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="110" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W110" s="12"/>
     </row>
-    <row r="111" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="111" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W111" s="12"/>
     </row>
-    <row r="112" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="112" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W112" s="12"/>
     </row>
-    <row r="113" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="113" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W113" s="11"/>
     </row>
-    <row r="114" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="114" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W114" s="12"/>
     </row>
-    <row r="115" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="115" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W115" s="12"/>
     </row>
-    <row r="116" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="116" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W116" s="12"/>
     </row>
-    <row r="117" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="117" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W117" s="12"/>
     </row>
-    <row r="118" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="118" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W118" s="11"/>
     </row>
-    <row r="119" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="119" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W119" s="12"/>
     </row>
-    <row r="120" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="120" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W120" s="12"/>
     </row>
-    <row r="121" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="121" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W121" s="11"/>
     </row>
-    <row r="122" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="122" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W122" s="12"/>
     </row>
-    <row r="123" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="123" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W123" s="12"/>
     </row>
-    <row r="124" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="124" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W124" s="12"/>
     </row>
-    <row r="125" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="125" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W125" s="12"/>
     </row>
-    <row r="126" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="126" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W126" s="11"/>
     </row>
-    <row r="127" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="127" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W127" s="12"/>
     </row>
-    <row r="128" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="128" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W128" s="12"/>
     </row>
-    <row r="129" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="129" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W129" s="12"/>
     </row>
-    <row r="130" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="130" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W130" s="11"/>
     </row>
-    <row r="131" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="131" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W131" s="12"/>
     </row>
-    <row r="132" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="132" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W132" s="12"/>
     </row>
-    <row r="133" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="133" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W133" s="12"/>
     </row>
-    <row r="134" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="134" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W134" s="11"/>
     </row>
-    <row r="135" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="135" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W135" s="12"/>
     </row>
-    <row r="136" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="136" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W136" s="12"/>
     </row>
-    <row r="137" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="137" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W137" s="12"/>
     </row>
-    <row r="138" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="138" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W138" s="12"/>
     </row>
-    <row r="139" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="139" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W139" s="11"/>
     </row>
-    <row r="140" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="140" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W140" s="12"/>
     </row>
-    <row r="141" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="141" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W141" s="12"/>
     </row>
-    <row r="142" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="142" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W142" s="12"/>
     </row>
-    <row r="143" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="143" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W143" s="12"/>
     </row>
-    <row r="144" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="144" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W144" s="12"/>
     </row>
-    <row r="145" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="145" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W145" s="11"/>
     </row>
-    <row r="146" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="146" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W146" s="12"/>
     </row>
-    <row r="147" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="147" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W147" s="12"/>
     </row>
-    <row r="148" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="148" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W148" s="12"/>
     </row>
-    <row r="149" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="149" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W149" s="11"/>
     </row>
-    <row r="150" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="150" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W150" s="12"/>
     </row>
-    <row r="151" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="151" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W151" s="12"/>
     </row>
-    <row r="152" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="152" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W152" s="12"/>
     </row>
-    <row r="153" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="153" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W153" s="12"/>
     </row>
-    <row r="154" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="154" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W154" s="11"/>
     </row>
-    <row r="155" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="155" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W155" s="12"/>
     </row>
-    <row r="156" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="156" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W156" s="12"/>
     </row>
-    <row r="157" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="157" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W157" s="12"/>
     </row>
-    <row r="158" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="158" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W158" s="12"/>
     </row>
-    <row r="159" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="159" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W159" s="11"/>
     </row>
-    <row r="160" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="160" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W160" s="12"/>
     </row>
-    <row r="161" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="161" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W161" s="12"/>
     </row>
-    <row r="162" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="162" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W162" s="12"/>
     </row>
-    <row r="163" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="163" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W163" s="12"/>
     </row>
-    <row r="164" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="164" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W164" s="12"/>
     </row>
-    <row r="165" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="165" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W165" s="12"/>
     </row>
-    <row r="166" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="166" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W166" s="12"/>
     </row>
-    <row r="167" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="167" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W167" s="12"/>
     </row>
-    <row r="168" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="168" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W168" s="12"/>
     </row>
-    <row r="169" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="169" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W169" s="12"/>
     </row>
-    <row r="170" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="170" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W170" s="11"/>
     </row>
-    <row r="171" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="171" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W171" s="12"/>
     </row>
-    <row r="172" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="172" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W172" s="12"/>
     </row>
-    <row r="173" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="173" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W173" s="11"/>
     </row>
-    <row r="174" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="174" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W174" s="12"/>
     </row>
-    <row r="175" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="175" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W175" s="12"/>
     </row>
-    <row r="176" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="176" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W176" s="12"/>
     </row>
-    <row r="177" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="177" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W177" s="11"/>
     </row>
-    <row r="178" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="178" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W178" s="12"/>
     </row>
-    <row r="179" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="179" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W179" s="12"/>
     </row>
-    <row r="180" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="180" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W180" s="12"/>
     </row>
-    <row r="181" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="181" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W181" s="12"/>
     </row>
-    <row r="182" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="182" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W182" s="12"/>
     </row>
-    <row r="183" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="183" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W183" s="11"/>
     </row>
-    <row r="184" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="184" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W184" s="12"/>
     </row>
-    <row r="185" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="185" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W185" s="12"/>
     </row>
-    <row r="186" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="186" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W186" s="11"/>
     </row>
-    <row r="187" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="187" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W187" s="12"/>
     </row>
-    <row r="188" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="188" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W188" s="12"/>
     </row>
-    <row r="189" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="189" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W189" s="12"/>
     </row>
-    <row r="190" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="190" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W190" s="12"/>
     </row>
-    <row r="191" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="191" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W191" s="11"/>
     </row>
-    <row r="192" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="192" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W192" s="12"/>
     </row>
-    <row r="193" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="193" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W193" s="12"/>
     </row>
-    <row r="194" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="194" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W194" s="12"/>
     </row>
-    <row r="195" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="195" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W195" s="12"/>
     </row>
-    <row r="196" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="196" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W196" s="12"/>
     </row>
-    <row r="197" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="197" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W197" s="11"/>
     </row>
-    <row r="198" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="198" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W198" s="12"/>
     </row>
-    <row r="199" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="199" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W199" s="12"/>
     </row>
-    <row r="200" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="200" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W200" s="12"/>
     </row>
   </sheetData>
